--- a/demo-data/olivine_demo_swift.xlsx
+++ b/demo-data/olivine_demo_swift.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2316</v>
+        <v>785</v>
       </c>
       <c r="H2" t="n">
-        <v>2871.53</v>
+        <v>6614.64</v>
       </c>
       <c r="I2" t="n">
-        <v>430.73</v>
+        <v>992.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3302.26</v>
+        <v>7606.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1701</v>
+        <v>2976</v>
       </c>
       <c r="H3" t="n">
-        <v>6283.03</v>
+        <v>2618.56</v>
       </c>
       <c r="I3" t="n">
-        <v>942.45</v>
+        <v>392.78</v>
       </c>
       <c r="J3" t="n">
-        <v>7225.48</v>
+        <v>3011.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -611,22 +611,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2566</v>
+        <v>2589</v>
       </c>
       <c r="H4" t="n">
-        <v>2419.85</v>
+        <v>3155.52</v>
       </c>
       <c r="I4" t="n">
-        <v>362.98</v>
+        <v>473.33</v>
       </c>
       <c r="J4" t="n">
-        <v>2782.83</v>
+        <v>3628.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,22 +655,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>648</v>
+        <v>544</v>
       </c>
       <c r="H5" t="n">
-        <v>3246.79</v>
+        <v>5650.03</v>
       </c>
       <c r="I5" t="n">
-        <v>487.02</v>
+        <v>847.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3733.81</v>
+        <v>6497.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1515</v>
+        <v>2266</v>
       </c>
       <c r="H6" t="n">
-        <v>5692.23</v>
+        <v>5857.28</v>
       </c>
       <c r="I6" t="n">
-        <v>853.83</v>
+        <v>878.59</v>
       </c>
       <c r="J6" t="n">
-        <v>6546.06</v>
+        <v>6735.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1131</v>
+        <v>2693</v>
       </c>
       <c r="H7" t="n">
-        <v>2807.37</v>
+        <v>4873.16</v>
       </c>
       <c r="I7" t="n">
-        <v>421.11</v>
+        <v>730.97</v>
       </c>
       <c r="J7" t="n">
-        <v>3228.48</v>
+        <v>5604.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2660</v>
+        <v>3070</v>
       </c>
       <c r="H8" t="n">
-        <v>3043.48</v>
+        <v>6368.93</v>
       </c>
       <c r="I8" t="n">
-        <v>456.52</v>
+        <v>955.34</v>
       </c>
       <c r="J8" t="n">
-        <v>3500</v>
+        <v>7324.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2425</v>
+        <v>2547</v>
       </c>
       <c r="H9" t="n">
-        <v>5371.34</v>
+        <v>6154.52</v>
       </c>
       <c r="I9" t="n">
-        <v>805.7</v>
+        <v>923.1799999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>6177.04</v>
+        <v>7077.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,22 +875,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1031</v>
+        <v>3081</v>
       </c>
       <c r="H10" t="n">
-        <v>3208.54</v>
+        <v>2930.89</v>
       </c>
       <c r="I10" t="n">
-        <v>481.28</v>
+        <v>439.63</v>
       </c>
       <c r="J10" t="n">
-        <v>3689.82</v>
+        <v>3370.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -919,22 +919,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3039</v>
+        <v>770</v>
       </c>
       <c r="H11" t="n">
-        <v>3818.37</v>
+        <v>4914.72</v>
       </c>
       <c r="I11" t="n">
-        <v>572.76</v>
+        <v>737.21</v>
       </c>
       <c r="J11" t="n">
-        <v>4391.13</v>
+        <v>5651.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -963,22 +963,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2206</v>
+        <v>2822</v>
       </c>
       <c r="H12" t="n">
-        <v>3865.17</v>
+        <v>4740.4</v>
       </c>
       <c r="I12" t="n">
-        <v>579.78</v>
+        <v>711.0599999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>4444.95</v>
+        <v>5451.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1007,22 +1007,22 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1058</v>
+        <v>1406</v>
       </c>
       <c r="H13" t="n">
-        <v>5933.72</v>
+        <v>2933.64</v>
       </c>
       <c r="I13" t="n">
-        <v>890.0599999999999</v>
+        <v>440.05</v>
       </c>
       <c r="J13" t="n">
-        <v>6823.78</v>
+        <v>3373.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1250</v>
+        <v>1503</v>
       </c>
       <c r="H14" t="n">
-        <v>2916.54</v>
+        <v>5363.33</v>
       </c>
       <c r="I14" t="n">
-        <v>437.48</v>
+        <v>804.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3354.02</v>
+        <v>6167.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1095,22 +1095,22 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1732</v>
+        <v>1189</v>
       </c>
       <c r="H15" t="n">
-        <v>2659.31</v>
+        <v>5131.68</v>
       </c>
       <c r="I15" t="n">
-        <v>398.9</v>
+        <v>769.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3058.21</v>
+        <v>5901.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1139,22 +1139,22 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>995</v>
+        <v>2706</v>
       </c>
       <c r="H16" t="n">
-        <v>3037.29</v>
+        <v>6357.5</v>
       </c>
       <c r="I16" t="n">
-        <v>455.59</v>
+        <v>953.62</v>
       </c>
       <c r="J16" t="n">
-        <v>3492.88</v>
+        <v>7311.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1183,16 +1183,148 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2370</v>
+        <v>504</v>
       </c>
       <c r="H17" t="n">
-        <v>5248.94</v>
+        <v>3241.02</v>
       </c>
       <c r="I17" t="n">
-        <v>787.34</v>
+        <v>486.15</v>
       </c>
       <c r="J17" t="n">
-        <v>6036.28</v>
+        <v>3727.17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hypery</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CN-19900</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SR-4516</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pietheo Investments</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2012</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I18" t="n">
+        <v>615</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4715</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CN-19901</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SR-4517</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TM Retailers</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bulawayo</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2761</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3050</v>
+      </c>
+      <c r="I19" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3507.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Olivine</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CN-19902</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SR-4518</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PNP Stores</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mutare</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1199</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3720</v>
+      </c>
+      <c r="I20" t="n">
+        <v>558</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4278</v>
       </c>
     </row>
   </sheetData>
